--- a/01-Requirements/05-Acceptance_Criteria.xlsx
+++ b/01-Requirements/05-Acceptance_Criteria.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\my things\SQA projects\QADemo E-Commerce Application Manual Testing\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\my things\SQA projects\QADemo E-Commerce Application Manual Testing\QADemoE-CommerceApplicationManualTesting\01-Requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3F226C3-652A-4973-BE9F-6714C2EA64BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76679FEB-1168-4120-91B7-E5B531AE7B76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="164">
   <si>
     <t>Key</t>
   </si>
@@ -72,30 +72,6 @@
     <t>Acceptance Criteria</t>
   </si>
   <si>
-    <t>AC-006-12</t>
-  </si>
-  <si>
-    <t>AC-006-11</t>
-  </si>
-  <si>
-    <t>AC-006-10</t>
-  </si>
-  <si>
-    <t>AC-006-09</t>
-  </si>
-  <si>
-    <t>AC-006-08</t>
-  </si>
-  <si>
-    <t>AC-006-07</t>
-  </si>
-  <si>
-    <t>AC-006-06</t>
-  </si>
-  <si>
-    <t>AC-006-05</t>
-  </si>
-  <si>
     <t>AC-006-04</t>
   </si>
   <si>
@@ -120,9 +96,6 @@
     <t>AC-005-01</t>
   </si>
   <si>
-    <t>AC-004-06</t>
-  </si>
-  <si>
     <t>AC-004-05</t>
   </si>
   <si>
@@ -138,66 +111,9 @@
     <t>AC-004-01</t>
   </si>
   <si>
-    <t>AC-003-12</t>
-  </si>
-  <si>
-    <t>AC-003-11</t>
-  </si>
-  <si>
-    <t>AC-003-10</t>
-  </si>
-  <si>
-    <t>AC-003-09</t>
-  </si>
-  <si>
-    <t>AC-003-08</t>
-  </si>
-  <si>
-    <t>AC-003-07</t>
-  </si>
-  <si>
-    <t>AC-003-06</t>
-  </si>
-  <si>
-    <t>AC-003-05</t>
-  </si>
-  <si>
-    <t>AC-003-04</t>
-  </si>
-  <si>
-    <t>AC-003-03</t>
-  </si>
-  <si>
-    <t>AC-003-02</t>
-  </si>
-  <si>
     <t>AC-003-01</t>
   </si>
   <si>
-    <t>AC-002-12</t>
-  </si>
-  <si>
-    <t>AC-002-11</t>
-  </si>
-  <si>
-    <t>AC-002-10</t>
-  </si>
-  <si>
-    <t>AC-002-09</t>
-  </si>
-  <si>
-    <t>AC-002-08</t>
-  </si>
-  <si>
-    <t>AC-002-07</t>
-  </si>
-  <si>
-    <t>AC-002-06</t>
-  </si>
-  <si>
-    <t>AC-002-05</t>
-  </si>
-  <si>
     <t>AC-002-04</t>
   </si>
   <si>
@@ -210,9 +126,6 @@
     <t>AC-002-01</t>
   </si>
   <si>
-    <t>AC-001-06</t>
-  </si>
-  <si>
     <t>AC-001-05</t>
   </si>
   <si>
@@ -228,18 +141,6 @@
     <t>AC-001-01</t>
   </si>
   <si>
-    <t>US-006-06</t>
-  </si>
-  <si>
-    <t>US-006-05</t>
-  </si>
-  <si>
-    <t>US-006-04</t>
-  </si>
-  <si>
-    <t>US-006-03</t>
-  </si>
-  <si>
     <t>US-006-02</t>
   </si>
   <si>
@@ -261,34 +162,7 @@
     <t>US-004-01</t>
   </si>
   <si>
-    <t>US-003-06</t>
-  </si>
-  <si>
-    <t>US-003-05</t>
-  </si>
-  <si>
-    <t>US-003-04</t>
-  </si>
-  <si>
-    <t>US-003-03</t>
-  </si>
-  <si>
-    <t>US-003-02</t>
-  </si>
-  <si>
     <t>US-003-01</t>
-  </si>
-  <si>
-    <t>US-002-06</t>
-  </si>
-  <si>
-    <t>US-002-05</t>
-  </si>
-  <si>
-    <t>US-002-04</t>
-  </si>
-  <si>
-    <t>US-002-03</t>
   </si>
   <si>
     <t>US-002-02</t>
@@ -389,11 +263,6 @@
 then the customer should be logged in successfully.</t>
   </si>
   <si>
-    <t>Given the customer has logged in successfully, 
-when authentication is completed, 
-then the customer should be redirected to the appropriate authenticated page.</t>
-  </si>
-  <si>
     <t>Given the customer is on the Login page, 
 when invalid or unregistered credentials are submitted, 
 then the system should reject the login attempt and display an appropriate error message.</t>
@@ -419,11 +288,6 @@
 then the system should display the available products with their relevant basic information.</t>
   </si>
   <si>
-    <t>Given the product list contains multiple products, 
-when the customer browses the list, 
-then the customer should be able to view the available products without missing or incorrectly duplicated product information.</t>
-  </si>
-  <si>
     <t>Given product categories are available, 
 when the customer selects a category, 
 then the system should display products belonging to the selected category.</t>
@@ -434,16 +298,6 @@
 then the system should clearly indicate that no products are available.</t>
   </si>
   <si>
-    <t>Given the customer is on the product search interface, 
-when the customer enters a relevant product keyword, 
-then the system should display matching products.</t>
-  </si>
-  <si>
-    <t>Given the customer searches using a keyword that does not match any product, 
-when the search is submitted, 
-then the system should indicate that no matching products were found.</t>
-  </si>
-  <si>
     <t>Given a product is available, 
 when the customer opens the product details, 
 then the system should display the product description.</t>
@@ -459,11 +313,6 @@
 then the system should display its current price.</t>
   </si>
   <si>
-    <t>Given the same product is viewed in different relevant purchase stages, 
-when the price is displayed, 
-then the displayed price should be consistent with the applicable product price.</t>
-  </si>
-  <si>
     <t>Given a product is available for purchase, 
 when the customer views the product details, 
 then the system should display appropriate availability information.</t>
@@ -479,21 +328,11 @@
 then the product should be added to the shopping cart.</t>
   </si>
   <si>
-    <t>Given a product has been added to the cart, 
-when the customer views the cart, 
-then the selected product and its applicable quantity and price should be displayed correctly.</t>
-  </si>
-  <si>
     <t>Given the customer has added one or more products to the cart, 
 when the customer opens the cart, 
 then the system should display all selected products with their relevant information.</t>
   </si>
   <si>
-    <t>Given the cart contains products, 
-when the customer views the cart, 
-then the displayed quantities, prices, and calculated total should correspond to the selected products.</t>
-  </si>
-  <si>
     <t>Given a product exists in the cart, 
 when the customer changes its quantity to a valid quantity, 
 then the cart should be updated with the new quantity.</t>
@@ -619,11 +458,6 @@
 then the system should display the total order amount.</t>
   </si>
   <si>
-    <t>Given the customer reviews an order amount, 
-when the total is displayed, 
-then it should correspond to the applicable products, quantities, and prices of that order.</t>
-  </si>
-  <si>
     <t>Given an order has been successfully placed, 
 when the customer views the order details, 
 then the system should display the delivery information associated with the order.</t>
@@ -645,13 +479,147 @@
   </si>
   <si>
     <t>Acceptance Criteria Document</t>
+  </si>
+  <si>
+    <t>Given the cart contains products, 
+when the customer views the cart, 
+then the displayed quantities, prices and calculated total should correspond to the selected products.</t>
+  </si>
+  <si>
+    <t>AC-005-05</t>
+  </si>
+  <si>
+    <t>AC-005-06</t>
+  </si>
+  <si>
+    <t>AC-005-07</t>
+  </si>
+  <si>
+    <t>AC-007-01</t>
+  </si>
+  <si>
+    <t>AC-007-02</t>
+  </si>
+  <si>
+    <t>AC-007-03</t>
+  </si>
+  <si>
+    <t>AC-007-04</t>
+  </si>
+  <si>
+    <t>AC-007-05</t>
+  </si>
+  <si>
+    <t>AC-007-06</t>
+  </si>
+  <si>
+    <t>AC-008-01</t>
+  </si>
+  <si>
+    <t>AC-008-02</t>
+  </si>
+  <si>
+    <t>AC-010-01</t>
+  </si>
+  <si>
+    <t>AC-009-01</t>
+  </si>
+  <si>
+    <t>AC-009-02</t>
+  </si>
+  <si>
+    <t>AC-010-02</t>
+  </si>
+  <si>
+    <t>AC-010-03</t>
+  </si>
+  <si>
+    <t>AC-010-04</t>
+  </si>
+  <si>
+    <t>AC-010-05</t>
+  </si>
+  <si>
+    <t>AC-010-06</t>
+  </si>
+  <si>
+    <t>AC-010-07</t>
+  </si>
+  <si>
+    <t>AC-010-08</t>
+  </si>
+  <si>
+    <t>AC-010-09</t>
+  </si>
+  <si>
+    <t>AC-010-10</t>
+  </si>
+  <si>
+    <t>AC-010-11</t>
+  </si>
+  <si>
+    <t>AC-010-12</t>
+  </si>
+  <si>
+    <t>US-005-03</t>
+  </si>
+  <si>
+    <t>US-005-04</t>
+  </si>
+  <si>
+    <t>US-007-01</t>
+  </si>
+  <si>
+    <t>US-007-02</t>
+  </si>
+  <si>
+    <t>US-007-03</t>
+  </si>
+  <si>
+    <t>US-008-01</t>
+  </si>
+  <si>
+    <t>US-009-01</t>
+  </si>
+  <si>
+    <t>US-010-01</t>
+  </si>
+  <si>
+    <t>US-010-02</t>
+  </si>
+  <si>
+    <t>US-010-03</t>
+  </si>
+  <si>
+    <t>US-010-04</t>
+  </si>
+  <si>
+    <t>US-010-05</t>
+  </si>
+  <si>
+    <t>US-010-06</t>
+  </si>
+  <si>
+    <t>Given the customer reviews an order amount, 
+when the total is displayed, 
+then it should correspond to the applicable products, quantities and prices of that order.</t>
+  </si>
+  <si>
+    <t>Given multiple products are available, 
+when the customer browses the product section, 
+then all available products should be displayed with their relevant information.</t>
+  </si>
+  <si>
+    <t>Given the customer searches using a keyword that does not match any available product, 
+when the search is submitted, 
+then the system should indicate that no matching products were found.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -671,6 +639,12 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -711,21 +685,21 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="10">
     <dxf>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -737,6 +711,9 @@
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -833,23 +810,23 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{09A174B0-A2BD-4CE1-ACFE-FDE5C4F398CA}" name="Table1" displayName="Table1" ref="A2:B7" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{09A174B0-A2BD-4CE1-ACFE-FDE5C4F398CA}" name="Table1" displayName="Table1" ref="A2:B7" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
   <autoFilter ref="A2:B7" xr:uid="{09A174B0-A2BD-4CE1-ACFE-FDE5C4F398CA}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{100BC1FB-57D5-4F52-BA19-A84D5413D7D9}" name="Key" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{C8F8B02B-A042-4AF2-84BD-8A048837E030}" name="Value" dataDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{100BC1FB-57D5-4F52-BA19-A84D5413D7D9}" name="Key" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{C8F8B02B-A042-4AF2-84BD-8A048837E030}" name="Value" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium25" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{92A619B3-D1BD-4B2D-A60B-AC3EBE2BC716}" name="Table2" displayName="Table2" ref="A13:D65" totalsRowShown="0" headerRowDxfId="4">
-  <autoFilter ref="A13:D65" xr:uid="{92A619B3-D1BD-4B2D-A60B-AC3EBE2BC716}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{92A619B3-D1BD-4B2D-A60B-AC3EBE2BC716}" name="Table2" displayName="Table2" ref="A13:D61" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
+  <autoFilter ref="A13:D61" xr:uid="{92A619B3-D1BD-4B2D-A60B-AC3EBE2BC716}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{FF660814-444D-42ED-A332-9A442DB36265}" name="AC ID" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{5BADF1B5-8AB7-4B5B-B683-75FEB95513BF}" name="User Story Title" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{E295F2A3-C5AB-4D0C-B508-8E983C03C6EC}" name="User Story ID" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{BA72A822-CC6F-41E8-AE34-904D13FBF009}" name="User Story ID" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{5BADF1B5-8AB7-4B5B-B683-75FEB95513BF}" name="User Story Title" dataDxfId="1"/>
     <tableColumn id="4" xr3:uid="{584899DF-013F-495B-97AA-22758381F1FF}" name="Acceptance Criteria" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium25" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1119,13 +1096,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:D65"/>
+  <dimension ref="A2:D61"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.77734375" customWidth="1"/>
-    <col min="3" max="3" width="17.21875" customWidth="1"/>
-    <col min="4" max="4" width="87.33203125" customWidth="1"/>
+    <col min="2" max="2" width="29.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.21875" customWidth="1"/>
+    <col min="4" max="4" width="86.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -1141,7 +1118,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>171</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -1181,744 +1158,689 @@
         <v>11</v>
       </c>
       <c r="B13" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>13</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>12</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A15" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A16" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A19" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A20" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A21" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A22" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A23" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A24" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A25" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A26" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A27" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A28" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A29" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A30" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C30" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="D30" s="6" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A31" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A32" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A33" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A34" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A35" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A36" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A37" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A38" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A39" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A40" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A41" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A42" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A43" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A44" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A45" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A46" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A47" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A48" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A49" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D49" s="6" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A50" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D50" s="6" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A51" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D51" s="6" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A52" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D52" s="6" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A53" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D53" s="6" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A54" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A55" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D55" s="6" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A56" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D56" s="6" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A57" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D57" s="6" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A58" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D58" s="6" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A59" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D59" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="C14" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="D14" s="7" t="s">
+    </row>
+    <row r="60" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A60" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D60" s="6" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A15" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="D15" s="7" t="s">
+    <row r="61" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A61" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D61" s="6" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A16" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A17" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A19" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A20" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A22" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A23" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A24" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A25" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A26" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A27" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A28" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A29" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A30" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A31" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A32" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A33" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A34" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A35" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A36" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="D36" s="7" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A37" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A38" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="C38" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="D38" s="7" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A39" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="D39" s="7" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A40" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="D40" s="7" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A41" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="D41" s="7" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A42" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="C42" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="D42" s="7" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A43" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="C43" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="D43" s="7" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A44" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="C44" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="D44" s="7" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A45" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="C45" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="D45" s="7" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A46" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="C46" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="D46" s="7" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A47" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="C47" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="D47" s="7" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A48" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C48" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="D48" s="7" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A49" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C49" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="D49" s="7" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A50" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="C50" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="D50" s="7" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A51" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="C51" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="D51" s="7" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A52" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="C52" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="D52" s="7" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A53" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="C53" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="D53" s="7" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A54" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="C54" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="D54" s="7" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A55" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="C55" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="D55" s="7" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A56" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C56" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="D56" s="7" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A57" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C57" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="D57" s="7" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A58" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="C58" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="D58" s="7" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A59" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="C59" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="D59" s="7" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A60" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="C60" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="D60" s="7" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A61" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="C61" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="D61" s="7" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A62" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="C62" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="D62" s="7" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A63" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="C63" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="D63" s="7" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A64" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="C64" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="D64" s="7" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A65" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="C65" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="D65" s="7" t="s">
-        <v>170</v>
-      </c>
-    </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="B5" r:id="rId1" xr:uid="{9DF5F7EF-76E4-48E8-81CC-1D25EA4C6224}"/>
   </hyperlinks>

--- a/01-Requirements/05-Acceptance_Criteria.xlsx
+++ b/01-Requirements/05-Acceptance_Criteria.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\my things\SQA projects\QADemo E-Commerce Application Manual Testing\QADemoE-CommerceApplicationManualTesting\01-Requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76679FEB-1168-4120-91B7-E5B531AE7B76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B48DDE41-F255-404F-90E5-B13AEB08DED1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -478,9 +478,6 @@
 then the displayed status should reflect the latest applicable order status.</t>
   </si>
   <si>
-    <t>Acceptance Criteria Document</t>
-  </si>
-  <si>
     <t>Given the cart contains products, 
 when the customer views the cart, 
 then the displayed quantities, prices and calculated total should correspond to the selected products.</t>
@@ -613,6 +610,9 @@
     <t>Given the customer searches using a keyword that does not match any available product, 
 when the search is submitted, 
 then the system should indicate that no matching products were found.</t>
+  </si>
+  <si>
+    <t>Acceptance Criterias</t>
   </si>
 </sst>
 </file>
@@ -1118,7 +1118,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>121</v>
+        <v>163</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -1262,7 +1262,7 @@
         <v>73</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
@@ -1304,7 +1304,7 @@
         <v>71</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
@@ -1416,7 +1416,7 @@
         <v>66</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
@@ -1424,7 +1424,7 @@
         <v>19</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>65</v>
@@ -1435,10 +1435,10 @@
     </row>
     <row r="33" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>65</v>
@@ -1449,10 +1449,10 @@
     </row>
     <row r="34" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>64</v>
@@ -1463,10 +1463,10 @@
     </row>
     <row r="35" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>64</v>
@@ -1533,10 +1533,10 @@
     </row>
     <row r="40" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>61</v>
@@ -1547,10 +1547,10 @@
     </row>
     <row r="41" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>61</v>
@@ -1561,10 +1561,10 @@
     </row>
     <row r="42" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C42" s="5" t="s">
         <v>60</v>
@@ -1575,10 +1575,10 @@
     </row>
     <row r="43" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C43" s="5" t="s">
         <v>60</v>
@@ -1589,10 +1589,10 @@
     </row>
     <row r="44" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C44" s="5" t="s">
         <v>59</v>
@@ -1603,10 +1603,10 @@
     </row>
     <row r="45" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C45" s="5" t="s">
         <v>59</v>
@@ -1617,10 +1617,10 @@
     </row>
     <row r="46" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C46" s="5" t="s">
         <v>58</v>
@@ -1631,10 +1631,10 @@
     </row>
     <row r="47" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C47" s="5" t="s">
         <v>58</v>
@@ -1645,10 +1645,10 @@
     </row>
     <row r="48" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C48" s="5" t="s">
         <v>57</v>
@@ -1659,10 +1659,10 @@
     </row>
     <row r="49" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C49" s="5" t="s">
         <v>57</v>
@@ -1673,10 +1673,10 @@
     </row>
     <row r="50" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C50" s="5" t="s">
         <v>56</v>
@@ -1687,10 +1687,10 @@
     </row>
     <row r="51" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C51" s="5" t="s">
         <v>56</v>
@@ -1701,10 +1701,10 @@
     </row>
     <row r="52" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C52" s="5" t="s">
         <v>55</v>
@@ -1715,10 +1715,10 @@
     </row>
     <row r="53" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A53" s="5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C53" s="5" t="s">
         <v>55</v>
@@ -1729,10 +1729,10 @@
     </row>
     <row r="54" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A54" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C54" s="5" t="s">
         <v>54</v>
@@ -1743,10 +1743,10 @@
     </row>
     <row r="55" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A55" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C55" s="5" t="s">
         <v>54</v>
@@ -1757,10 +1757,10 @@
     </row>
     <row r="56" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A56" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C56" s="5" t="s">
         <v>53</v>
@@ -1771,24 +1771,24 @@
     </row>
     <row r="57" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A57" s="5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C57" s="5" t="s">
         <v>53</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A58" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C58" s="5" t="s">
         <v>52</v>
@@ -1799,10 +1799,10 @@
     </row>
     <row r="59" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A59" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C59" s="5" t="s">
         <v>52</v>
@@ -1813,10 +1813,10 @@
     </row>
     <row r="60" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A60" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C60" s="5" t="s">
         <v>51</v>
@@ -1827,10 +1827,10 @@
     </row>
     <row r="61" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C61" s="5" t="s">
         <v>51</v>
